--- a/Foglio_ore_template.xlsx
+++ b/Foglio_ore_template.xlsx
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="C18" s="77">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D18" s="77">
         <f>(B18+B19)*C18</f>
@@ -1805,7 +1805,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="77">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D20" s="77">
         <f>(B20+B21)*C20</f>
@@ -1869,7 +1869,7 @@
         <v>0</v>
       </c>
       <c r="C22" s="42">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D22" s="42">
         <f>C22*B22</f>
@@ -1947,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="C24" s="42">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D24" s="42">
         <f>C24*B24</f>
@@ -1981,7 +1981,7 @@
         <v>0</v>
       </c>
       <c r="C25" s="42">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D25" s="42">
         <f>C25*B25</f>
